--- a/data-source/武器数据7_4_0.xlsx
+++ b/data-source/武器数据7_4_0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jasonX\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383AC40F-BA5E-40D2-A35E-2D2061B48D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAEFC674-1E01-436A-A16F-E8FC6C14A66F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CD8BDD62-74D8-4CB5-8775-A0C7E48D0400}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="289">
   <si>
     <t>武器</t>
   </si>
@@ -414,12 +414,6 @@
   </si>
   <si>
     <t>战锤</t>
-  </si>
-  <si>
-    <t>40真伤</t>
-  </si>
-  <si>
-    <t>无视敌人护甲</t>
   </si>
   <si>
     <t>骨制棒子</t>
@@ -927,6 +921,9 @@
   <si>
     <t>钢锭*20 魔法皮革*15 桦木板*20 
 屠杀卷轴*1</t>
+  </si>
+  <si>
+    <t>无视敌人200护甲</t>
   </si>
 </sst>
 </file>
@@ -1441,12 +1438,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1795,16 +1792,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.4" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="42" t="s">
-        <v>282</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
+      <c r="A1" s="44" t="s">
+        <v>280</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
     </row>
     <row r="2" spans="1:8" ht="13.9" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2944,8 +2941,8 @@
       <c r="A52" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="B52" s="15" t="s">
-        <v>126</v>
+      <c r="B52" s="15">
+        <v>80</v>
       </c>
       <c r="C52" s="19"/>
       <c r="D52" s="15">
@@ -2959,12 +2956,12 @@
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="13" t="s">
-        <v>127</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B53" s="15">
         <v>42</v>
@@ -2984,10 +2981,10 @@
     </row>
     <row r="54" spans="1:9" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C54" s="19"/>
       <c r="D54" s="15">
@@ -3000,16 +2997,16 @@
         <v>72</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H54" s="10"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="14" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C55" s="19"/>
       <c r="D55" s="15">
@@ -3026,7 +3023,7 @@
     </row>
     <row r="56" spans="1:9" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B56" s="15">
         <v>45</v>
@@ -3042,16 +3039,16 @@
         <v>35</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H56" s="10"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C57" s="19"/>
       <c r="D57" s="15">
@@ -3065,15 +3062,15 @@
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="35" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="21" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C58" s="19"/>
       <c r="D58" s="15">
@@ -3087,19 +3084,19 @@
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="I58" s="43"/>
+        <v>286</v>
+      </c>
+      <c r="I58" s="42"/>
     </row>
     <row r="59" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A59" s="20" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B59" s="15">
         <v>50</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D59" s="15">
         <v>1</v>
@@ -3112,12 +3109,12 @@
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="13" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="20" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B60" s="15">
         <v>52</v>
@@ -3134,12 +3131,12 @@
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="23" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="24" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B61" s="15">
         <v>55</v>
@@ -3155,13 +3152,13 @@
         <v>35</v>
       </c>
       <c r="G61" s="25" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H61" s="26"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="20" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B62" s="15">
         <v>55</v>
@@ -3178,12 +3175,12 @@
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B63" s="15">
         <v>55</v>
@@ -3202,15 +3199,15 @@
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="13" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="20" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C64" s="19"/>
       <c r="D64" s="15">
@@ -3224,15 +3221,15 @@
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="20" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C65" s="19"/>
       <c r="D65" s="15">
@@ -3246,15 +3243,15 @@
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="27" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C66" s="19"/>
       <c r="D66" s="15">
@@ -3267,16 +3264,16 @@
         <v>56</v>
       </c>
       <c r="G66" s="25" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H66" s="10"/>
     </row>
     <row r="67" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C67" s="19"/>
       <c r="D67" s="15">
@@ -3293,10 +3290,10 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="14" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C68" s="19"/>
       <c r="D68" s="15">
@@ -3313,7 +3310,7 @@
     </row>
     <row r="69" spans="1:8" ht="43.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B69" s="15">
         <v>60</v>
@@ -3330,15 +3327,15 @@
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="28" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="20" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C70" s="19"/>
       <c r="D70" s="15">
@@ -3355,10 +3352,10 @@
     </row>
     <row r="71" spans="1:8" ht="44.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C71" s="19"/>
       <c r="D71" s="15">
@@ -3372,18 +3369,18 @@
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="28" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B72" s="15">
         <v>60</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D72" s="15">
         <v>1</v>
@@ -3401,13 +3398,13 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="20" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B73" s="15">
         <v>60</v>
       </c>
       <c r="C73" s="16" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D73" s="15">
         <v>0.9</v>
@@ -3420,18 +3417,18 @@
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="20" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D74" s="15">
         <v>1.1000000000000001</v>
@@ -3444,18 +3441,18 @@
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D75" s="15">
         <v>1.1000000000000001</v>
@@ -3468,15 +3465,15 @@
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C76" s="19"/>
       <c r="D76" s="15">
@@ -3489,13 +3486,13 @@
         <v>59</v>
       </c>
       <c r="G76" s="29" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H76" s="30"/>
     </row>
     <row r="77" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="20" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B77" s="15">
         <v>62</v>
@@ -3512,15 +3509,15 @@
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="28" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="27.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="22" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C78" s="19"/>
       <c r="D78" s="15">
@@ -3533,18 +3530,18 @@
         <v>56</v>
       </c>
       <c r="G78" s="25" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H78" s="31" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C79" s="19"/>
       <c r="D79" s="15">
@@ -3557,18 +3554,18 @@
         <v>56</v>
       </c>
       <c r="G79" s="25" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H79" s="31" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C80" s="19"/>
       <c r="D80" s="15">
@@ -3581,16 +3578,16 @@
         <v>56</v>
       </c>
       <c r="G80" s="25" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H80" s="10"/>
     </row>
     <row r="81" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C81" s="19"/>
       <c r="D81" s="15">
@@ -3604,12 +3601,12 @@
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="28" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="14" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B82" s="15">
         <v>65</v>
@@ -3629,7 +3626,7 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B83" s="15">
         <v>65</v>
@@ -3649,10 +3646,10 @@
     </row>
     <row r="84" spans="1:8" ht="30.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="22" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C84" s="19"/>
       <c r="D84" s="15">
@@ -3665,18 +3662,18 @@
         <v>59</v>
       </c>
       <c r="G84" s="29" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H84" s="31" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C85" s="19"/>
       <c r="D85" s="15">
@@ -3693,10 +3690,10 @@
     </row>
     <row r="86" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A86" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C86" s="19"/>
       <c r="D86" s="15">
@@ -3713,10 +3710,10 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="14" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C87" s="19"/>
       <c r="D87" s="15">
@@ -3733,13 +3730,13 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="21" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C88" s="17" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D88" s="15">
         <v>0.9</v>
@@ -3752,18 +3749,18 @@
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="32" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="21" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B89" s="15">
         <v>70</v>
       </c>
       <c r="C89" s="16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D89" s="15">
         <v>0.8</v>
@@ -3776,12 +3773,12 @@
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="33" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B90" s="15">
         <v>77</v>
@@ -3798,12 +3795,12 @@
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="21" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B91" s="15">
         <v>80</v>
@@ -3820,15 +3817,15 @@
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="28" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="13.9" x14ac:dyDescent="0.35">
       <c r="A92" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C92" s="19"/>
       <c r="D92" s="15">
@@ -3845,10 +3842,10 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C93" s="19"/>
       <c r="D93" s="15">
@@ -3865,13 +3862,13 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="21" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C94" s="16" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D94" s="15">
         <v>0.9</v>
@@ -3884,18 +3881,18 @@
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="21" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C95" s="17" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D95" s="15">
         <v>0.9</v>
@@ -3911,7 +3908,7 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="21" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B96" s="15">
         <v>83</v>
@@ -3928,15 +3925,15 @@
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="20" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C97" s="19"/>
       <c r="D97" s="15">
@@ -3950,15 +3947,15 @@
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="34" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C98" s="19"/>
       <c r="D98" s="15">
@@ -3975,7 +3972,7 @@
     </row>
     <row r="99" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="14" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B99" s="15">
         <v>90</v>
@@ -3991,13 +3988,13 @@
         <v>29</v>
       </c>
       <c r="G99" s="29" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H99" s="10"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="20" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B100" s="15">
         <v>90</v>
@@ -4014,12 +4011,12 @@
       </c>
       <c r="G100" s="7"/>
       <c r="H100" s="13" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="21" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B101" s="15">
         <v>90</v>
@@ -4036,15 +4033,15 @@
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="21" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C102" s="19"/>
       <c r="D102" s="15">
@@ -4058,12 +4055,12 @@
       </c>
       <c r="G102" s="7"/>
       <c r="H102" s="13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="21" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B103" s="15">
         <v>95</v>
@@ -4080,12 +4077,12 @@
       </c>
       <c r="G103" s="7"/>
       <c r="H103" s="28" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="21" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B104" s="15">
         <v>98</v>
@@ -4102,12 +4099,12 @@
       </c>
       <c r="G104" s="7"/>
       <c r="H104" s="28" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="21" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B105" s="15">
         <v>100</v>
@@ -4124,18 +4121,18 @@
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="28" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A106" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="B106" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="C106" s="18" t="s">
         <v>241</v>
-      </c>
-      <c r="B106" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="C106" s="18" t="s">
-        <v>243</v>
       </c>
       <c r="D106" s="15">
         <v>0.8</v>
@@ -4148,12 +4145,12 @@
       </c>
       <c r="G106" s="7"/>
       <c r="H106" s="13" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="21" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B107" s="15">
         <v>100</v>
@@ -4170,15 +4167,15 @@
       </c>
       <c r="G107" s="7"/>
       <c r="H107" s="13" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="21" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C108" s="19"/>
       <c r="D108" s="15">
@@ -4192,15 +4189,15 @@
       </c>
       <c r="G108" s="7"/>
       <c r="H108" s="35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="21" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C109" s="19"/>
       <c r="D109" s="15">
@@ -4214,12 +4211,12 @@
       </c>
       <c r="G109" s="7"/>
       <c r="H109" s="13" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="21" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B110" s="15">
         <v>100</v>
@@ -4236,18 +4233,18 @@
       </c>
       <c r="G110" s="7"/>
       <c r="H110" s="13" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="21" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B111" s="15">
         <v>105</v>
       </c>
       <c r="C111" s="16" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D111" s="15">
         <v>0.8</v>
@@ -4260,18 +4257,18 @@
       </c>
       <c r="G111" s="7"/>
       <c r="H111" s="28" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="21" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B112" s="15">
         <v>105</v>
       </c>
       <c r="C112" s="17" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D112" s="15">
         <v>0.7</v>
@@ -4284,12 +4281,12 @@
       </c>
       <c r="G112" s="7"/>
       <c r="H112" s="28" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="20" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B113" s="15">
         <v>107</v>
@@ -4306,12 +4303,12 @@
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="35" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="21" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B114" s="15">
         <v>110</v>
@@ -4328,12 +4325,12 @@
       </c>
       <c r="G114" s="7"/>
       <c r="H114" s="13" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="21" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B115" s="15">
         <v>110</v>
@@ -4350,12 +4347,12 @@
       </c>
       <c r="G115" s="7"/>
       <c r="H115" s="35" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="21" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B116" s="15">
         <v>110</v>
@@ -4372,12 +4369,12 @@
       </c>
       <c r="G116" s="7"/>
       <c r="H116" s="35" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="21" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B117" s="15">
         <v>112</v>
@@ -4394,15 +4391,15 @@
       </c>
       <c r="G117" s="7"/>
       <c r="H117" s="13" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="B118" s="15" t="s">
         <v>285</v>
-      </c>
-      <c r="B118" s="15" t="s">
-        <v>287</v>
       </c>
       <c r="C118" s="19"/>
       <c r="D118" s="15">
@@ -4414,16 +4411,16 @@
       <c r="F118" s="15">
         <v>50</v>
       </c>
-      <c r="G118" s="44" t="s">
-        <v>289</v>
+      <c r="G118" s="43" t="s">
+        <v>287</v>
       </c>
       <c r="H118" s="28" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="21" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B119" s="15">
         <v>128</v>
@@ -4440,18 +4437,18 @@
       </c>
       <c r="G119" s="7"/>
       <c r="H119" s="13" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="36" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C120" s="17" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D120" s="15">
         <v>1</v>
@@ -4464,15 +4461,15 @@
       </c>
       <c r="G120" s="7"/>
       <c r="H120" s="31" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="121" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="21" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C121" s="19"/>
       <c r="D121" s="15">
@@ -4486,12 +4483,12 @@
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="31" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="21" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B122" s="15">
         <v>130</v>
@@ -4508,12 +4505,12 @@
       </c>
       <c r="G122" s="7"/>
       <c r="H122" s="35" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B123" s="15">
         <v>132</v>
@@ -4530,12 +4527,12 @@
       </c>
       <c r="G123" s="7"/>
       <c r="H123" s="28" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B124" s="15">
         <v>132</v>
@@ -4552,12 +4549,12 @@
       </c>
       <c r="G124" s="7"/>
       <c r="H124" s="28" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="21" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B125" s="15">
         <v>132</v>
@@ -4574,15 +4571,15 @@
       </c>
       <c r="G125" s="7"/>
       <c r="H125" s="28" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="13.9" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="37" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B126" s="38" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C126" s="39"/>
       <c r="D126" s="38">
@@ -4596,7 +4593,7 @@
       </c>
       <c r="G126" s="40"/>
       <c r="H126" s="41" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="13.9" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -4609,15 +4606,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F24FF01B6E691B418AC7A3AA007394EC" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="59dca28e393f34dbf2d8416fcf89659e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8f43ef-8ea4-412d-9c18-5388ad596486" xmlns:ns4="c1e77170-3c0a-491c-a033-5a7c184eabd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9fc4d359a4793fb93aa5c6a1e92df795" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
@@ -4836,6 +4824,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4845,14 +4842,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E7059C5-FC20-439B-9607-B11AF63F0499}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4867,6 +4856,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9617B4-669B-418F-85A1-00AF659D3A3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
